--- a/data/lista_productos.xlsx
+++ b/data/lista_productos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DUOC\2 año\4to Semestre\FullStack 2\leveup\Level-Up\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DUOC\2 año\4to Semestre\FullStack 2\leveup\Level-Up\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F033BAF-23D8-496A-89F5-AD661262329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F6907-8BA4-4A85-A215-8F2D6A2F8B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/lista_productos.xlsx
+++ b/data/lista_productos.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DUOC\2 año\4to Semestre\FullStack 2\leveup\Level-Up\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F6907-8BA4-4A85-A215-8F2D6A2F8B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F06506-695A-4D35-80F6-722A7AD27617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
+    <sheet name="productos" sheetId="1" r:id="rId1"/>
+    <sheet name="stock" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="153">
   <si>
     <t>id</t>
   </si>
@@ -41,9 +53,6 @@
   </si>
   <si>
     <t>Un clásico juego de estrategia donde los jugadores compiten por colonizar y expandirse en la isla de Catan. Ideal para 3-4 jugadores y perfecto para noches de juego en familia o con amigos</t>
-  </si>
-  <si>
-    <t>Juegos de mesa</t>
   </si>
   <si>
     <t>The Mind</t>
@@ -477,6 +486,12 @@
   <si>
     <t>https://graficacolectiva.cl/wp-content/uploads/2021/02/polera_sailor_2-1.jpg</t>
   </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>Juegos de Mesa</t>
+  </si>
 </sst>
 </file>
 
@@ -787,7 +802,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -824,10 +839,10 @@
         <v>29990</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -855,19 +870,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>18990</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -895,19 +910,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1">
         <v>19990</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -935,19 +950,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1">
         <v>17990</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -975,19 +990,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
         <v>17990</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1015,19 +1030,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1">
         <v>6990</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1055,19 +1070,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1">
         <v>15990</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1095,19 +1110,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1">
         <v>16990</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1135,19 +1150,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1">
         <v>29990</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1175,19 +1190,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1">
         <v>29990</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1215,19 +1230,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1">
         <v>29990</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1255,19 +1270,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>29990</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1295,19 +1310,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1">
         <v>29990</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1335,19 +1350,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1">
         <v>69990</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1375,19 +1390,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1">
         <v>29990</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1415,19 +1430,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="1">
         <v>29990</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1455,19 +1470,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1">
         <v>29990</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1495,19 +1510,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1">
         <v>29990</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1535,19 +1550,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
         <v>29990</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1575,19 +1590,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1">
         <v>29990</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1615,19 +1630,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1">
         <v>669990</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1655,19 +1670,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1">
         <v>229990</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1695,19 +1710,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="1">
         <v>659990</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1735,19 +1750,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1">
         <v>669990</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1775,19 +1790,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1">
         <v>4281990</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1815,19 +1830,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1">
         <v>1795990</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1855,19 +1870,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
         <v>659990</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -1895,19 +1910,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1">
         <v>1153990</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1935,19 +1950,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1">
         <v>1158990</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -1975,19 +1990,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1">
         <v>661990</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2015,19 +2030,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1">
         <v>399990</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2055,19 +2070,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="1">
         <v>639990</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2095,19 +2110,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1">
         <v>129990</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2135,19 +2150,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1">
         <v>129990</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2175,19 +2190,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
         <v>129990</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2215,19 +2230,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1">
         <v>149990</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2255,19 +2270,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1">
         <v>125990</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -2295,19 +2310,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="1">
         <v>139990</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2335,19 +2350,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="1">
         <v>119990</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2375,19 +2390,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1">
         <v>119990</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2415,19 +2430,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1">
         <v>119990</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2455,19 +2470,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="1">
         <v>84990</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -2495,19 +2510,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1">
         <v>59990</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2535,19 +2550,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1">
         <v>14990</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2575,19 +2590,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1">
         <v>29990</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2615,19 +2630,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="1">
         <v>29990</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2655,19 +2670,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="1">
         <v>29990</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2695,19 +2710,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D49" s="1">
         <v>29990</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2735,19 +2750,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1">
         <v>29990</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2775,19 +2790,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1">
         <v>29990</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2815,19 +2830,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1">
         <v>29990</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2855,19 +2870,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1">
         <v>29990</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2895,19 +2910,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="1">
         <v>29990</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2935,19 +2950,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" s="1">
         <v>29990</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2975,19 +2990,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" s="1">
         <v>29990</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -3015,19 +3030,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1">
         <v>19990</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -3055,19 +3070,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58" s="1">
         <v>19990</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -3095,19 +3110,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="1">
         <v>19990</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -3135,19 +3150,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60" s="1">
         <v>19990</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -3175,19 +3190,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1">
         <v>19990</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -3215,19 +3230,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1">
         <v>29990</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -3255,19 +3270,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D63" s="1">
         <v>29990</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -3295,19 +3310,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D64" s="1">
         <v>29990</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -3335,19 +3350,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D65" s="1">
         <v>29990</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -3375,19 +3390,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D66" s="1">
         <v>29990</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -3415,19 +3430,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D67" s="1">
         <v>29990</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -3455,19 +3470,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D68" s="1">
         <v>29990</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -3495,19 +3510,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" s="1">
         <v>29990</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -29601,4 +29616,566 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDB33F7-C918-4A55-A14B-5C2A47507D16}">
+  <dimension ref="A1:B69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>